--- a/output/pdf_financials_xlsx/PLZ.UN.xlsx
+++ b/output/pdf_financials_xlsx/PLZ.UN.xlsx
@@ -2220,40 +2220,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>25.28</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>6.37</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.744</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>5.182</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7.296</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>8.845000000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>8.061999999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>7.262</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>7.262</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>8.868</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>8.092000000000001</v>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
@@ -2316,40 +2316,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>25.28</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>6.37</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.744</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>5.182</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7.296</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>8.845000000000001</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>8.061999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>7.262</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>7.262</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>8.868</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>8.092000000000001</v>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
@@ -2892,40 +2892,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>38.884</v>
+        <v>13.604</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>22.838</v>
+        <v>16.468</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>32.498</v>
+        <v>29.754</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>18.938</v>
+        <v>13.756</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>20.764</v>
+        <v>14.514</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>23.34</v>
+        <v>16.044</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>20.985</v>
+        <v>12.14</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>19.503</v>
+        <v>11.441</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>40.974</v>
+        <v>33.712</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>40.974</v>
+        <v>33.712</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>21.54</v>
+        <v>12.672</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>54.466</v>
+        <v>46.374</v>
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">

--- a/output/pdf_financials_xlsx/PLZ.UN.xlsx
+++ b/output/pdf_financials_xlsx/PLZ.UN.xlsx
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-13.065</v>
+        <v>-12.972</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>141.446</v>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.093</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-56.001</v>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-13.065</v>
+        <v>-12.972</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>141.446</v>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-13.065</v>
+        <v>-12.972</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>141.446</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-15.72372459111095</v>
+        <v>-15.61179911181716</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>151.4800376970528</v>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.7169287696577243</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>39.5917876786901</v>
@@ -39280,7 +39280,11 @@
           <t>Share of profit of associates</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -41214,7 +41218,11 @@
           <t>Share of profit of associates (Note 5)</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -46190,7 +46198,11 @@
           <t>Share of profit (loss) of associates</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
           <t>-</t>
@@ -46549,7 +46561,11 @@
           <t>Income tax recovery (expense) total</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E508" s="5" t="n">
         <v>0.093</v>
       </c>
@@ -49357,7 +49373,11 @@
           <t>Share of profit of associates (Note 5)</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
           <t>-</t>
@@ -51684,7 +51704,11 @@
           <t>Share of profit (loss) of associates</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr"/>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E573" t="inlineStr">
         <is>
           <t>-</t>
@@ -56450,7 +56474,11 @@
           <t>Share of profit of associates</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
           <t>-</t>
@@ -61741,7 +61769,11 @@
           <t>Share of profit of associates</t>
         </is>
       </c>
-      <c r="D700" t="inlineStr"/>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E700" s="5" t="n">
         <v>1.307</v>
       </c>
